--- a/artfynd/A 44874-2025 artfynd.xlsx
+++ b/artfynd/A 44874-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441125</v>
+        <v>113441148</v>
       </c>
       <c r="B2" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698517</v>
+        <v>698608</v>
       </c>
       <c r="R2" t="n">
-        <v>7207466</v>
+        <v>7207330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441148</v>
+        <v>113441125</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698608</v>
+        <v>698517</v>
       </c>
       <c r="R3" t="n">
-        <v>7207330</v>
+        <v>7207466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
